--- a/Input/FantaSPL_V2.3.xlsx
+++ b/Input/FantaSPL_V2.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Local_Docs\Admin\Other\Kit\SPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE84CCD-6C2B-4871-B532-9CAB2366F98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FED7B2-5C3A-48DB-BF9B-73BBA4D962B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="11" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="111">
   <si>
     <t>Parameter</t>
   </si>
@@ -509,7 +509,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -579,6 +579,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1127,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29AA2D-3F32-45F2-B719-A1F62E0F1A5F}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="17.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="17.1796875" style="1"/>
@@ -1463,6 +1478,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="26">
+        <v>45170</v>
+      </c>
+      <c r="B31" s="27">
+        <v>10</v>
+      </c>
+      <c r="C31" s="27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="26">
+        <v>45179</v>
+      </c>
+      <c r="B32" s="27">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1470,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55E8A24-46F9-4225-A2C2-A9164F13364A}">
-  <dimension ref="A1:J422"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr defaultColWidth="17.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.453125" style="11" bestFit="1" customWidth="1"/>
@@ -13557,7 +13594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" s="7">
         <v>45119</v>
       </c>
@@ -13586,7 +13623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" s="7">
         <v>45119</v>
       </c>
@@ -13615,7 +13652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" s="7">
         <v>45119</v>
       </c>
@@ -13644,7 +13681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" s="7">
         <v>45119</v>
       </c>
@@ -13673,7 +13710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" s="7">
         <v>45119</v>
       </c>
@@ -13702,7 +13739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" s="7">
         <v>45119</v>
       </c>
@@ -13731,8 +13768,539 @@
         <v>0</v>
       </c>
     </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A423" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B423" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C423" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D423" s="30">
+        <v>0</v>
+      </c>
+      <c r="E423" s="30">
+        <v>0</v>
+      </c>
+      <c r="F423" s="30">
+        <v>0</v>
+      </c>
+      <c r="G423" s="30">
+        <v>0</v>
+      </c>
+      <c r="H423" s="30">
+        <v>0</v>
+      </c>
+      <c r="I423" s="30">
+        <v>0</v>
+      </c>
+      <c r="J423" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A424" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B424" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C424" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D424" s="30">
+        <v>3</v>
+      </c>
+      <c r="E424" s="30">
+        <v>0</v>
+      </c>
+      <c r="F424" s="30">
+        <v>0</v>
+      </c>
+      <c r="G424" s="30">
+        <v>0</v>
+      </c>
+      <c r="H424" s="30">
+        <v>0</v>
+      </c>
+      <c r="I424" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A425" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B425" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C425" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D425" s="30">
+        <v>1</v>
+      </c>
+      <c r="E425" s="30">
+        <v>0</v>
+      </c>
+      <c r="F425" s="30">
+        <v>0</v>
+      </c>
+      <c r="G425" s="30">
+        <v>0</v>
+      </c>
+      <c r="H425" s="30">
+        <v>0</v>
+      </c>
+      <c r="I425" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A426" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B426" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C426" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D426" s="30">
+        <v>0</v>
+      </c>
+      <c r="E426" s="30">
+        <v>0</v>
+      </c>
+      <c r="F426" s="30">
+        <v>0</v>
+      </c>
+      <c r="G426" s="30">
+        <v>0</v>
+      </c>
+      <c r="H426" s="30">
+        <v>0</v>
+      </c>
+      <c r="I426" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A427" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B427" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C427" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D427" s="30">
+        <v>0</v>
+      </c>
+      <c r="E427" s="30">
+        <v>0</v>
+      </c>
+      <c r="F427" s="30">
+        <v>0</v>
+      </c>
+      <c r="G427" s="30">
+        <v>0</v>
+      </c>
+      <c r="H427" s="30">
+        <v>0</v>
+      </c>
+      <c r="I427" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A428" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B428" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C428" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D428" s="30">
+        <v>3</v>
+      </c>
+      <c r="E428" s="30">
+        <v>0</v>
+      </c>
+      <c r="F428" s="30">
+        <v>0</v>
+      </c>
+      <c r="G428" s="30">
+        <v>0</v>
+      </c>
+      <c r="H428" s="30">
+        <v>0</v>
+      </c>
+      <c r="I428" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A429" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B429" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C429" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D429" s="30">
+        <v>2</v>
+      </c>
+      <c r="E429" s="30">
+        <v>0</v>
+      </c>
+      <c r="F429" s="30">
+        <v>0</v>
+      </c>
+      <c r="G429" s="30">
+        <v>0</v>
+      </c>
+      <c r="H429" s="30">
+        <v>0</v>
+      </c>
+      <c r="I429" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A430" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B430" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C430" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D430" s="30">
+        <v>0</v>
+      </c>
+      <c r="E430" s="30">
+        <v>0</v>
+      </c>
+      <c r="F430" s="30">
+        <v>0</v>
+      </c>
+      <c r="G430" s="30">
+        <v>0</v>
+      </c>
+      <c r="H430" s="30">
+        <v>0</v>
+      </c>
+      <c r="I430" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A431" s="28">
+        <v>45170</v>
+      </c>
+      <c r="B431" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C431" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D431" s="30">
+        <v>0</v>
+      </c>
+      <c r="E431" s="30">
+        <v>0</v>
+      </c>
+      <c r="F431" s="30">
+        <v>0</v>
+      </c>
+      <c r="G431" s="30">
+        <v>0</v>
+      </c>
+      <c r="H431" s="30">
+        <v>0</v>
+      </c>
+      <c r="I431" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A432" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B432" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C432" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D432" s="30">
+        <v>0</v>
+      </c>
+      <c r="E432" s="30">
+        <v>0</v>
+      </c>
+      <c r="F432" s="30">
+        <v>0</v>
+      </c>
+      <c r="G432" s="30">
+        <v>0</v>
+      </c>
+      <c r="H432" s="30">
+        <v>0</v>
+      </c>
+      <c r="I432" s="30">
+        <v>0</v>
+      </c>
+      <c r="J432" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A433" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B433" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C433" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D433" s="30">
+        <v>3</v>
+      </c>
+      <c r="E433" s="30">
+        <v>0</v>
+      </c>
+      <c r="F433" s="30">
+        <v>0</v>
+      </c>
+      <c r="G433" s="30">
+        <v>0</v>
+      </c>
+      <c r="H433" s="30">
+        <v>0</v>
+      </c>
+      <c r="I433" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A434" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B434" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C434" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D434" s="30">
+        <v>1</v>
+      </c>
+      <c r="E434" s="30">
+        <v>0</v>
+      </c>
+      <c r="F434" s="30">
+        <v>0</v>
+      </c>
+      <c r="G434" s="30">
+        <v>0</v>
+      </c>
+      <c r="H434" s="30">
+        <v>0</v>
+      </c>
+      <c r="I434" s="30">
+        <v>0</v>
+      </c>
+      <c r="J434" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A435" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B435" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C435" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D435" s="30">
+        <v>0</v>
+      </c>
+      <c r="E435" s="30">
+        <v>0</v>
+      </c>
+      <c r="F435" s="30">
+        <v>0</v>
+      </c>
+      <c r="G435" s="30">
+        <v>0</v>
+      </c>
+      <c r="H435" s="30">
+        <v>0</v>
+      </c>
+      <c r="I435" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A436" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B436" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C436" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D436" s="30">
+        <v>0</v>
+      </c>
+      <c r="E436" s="30">
+        <v>0</v>
+      </c>
+      <c r="F436" s="30">
+        <v>0</v>
+      </c>
+      <c r="G436" s="30">
+        <v>0</v>
+      </c>
+      <c r="H436" s="30">
+        <v>0</v>
+      </c>
+      <c r="I436" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A437" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B437" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C437" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D437" s="30">
+        <v>3</v>
+      </c>
+      <c r="E437" s="30">
+        <v>0</v>
+      </c>
+      <c r="F437" s="30">
+        <v>0</v>
+      </c>
+      <c r="G437" s="30">
+        <v>0</v>
+      </c>
+      <c r="H437" s="30">
+        <v>0</v>
+      </c>
+      <c r="I437" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A438" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B438" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C438" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D438" s="30">
+        <v>2</v>
+      </c>
+      <c r="E438" s="30">
+        <v>0</v>
+      </c>
+      <c r="F438" s="30">
+        <v>0</v>
+      </c>
+      <c r="G438" s="30">
+        <v>0</v>
+      </c>
+      <c r="H438" s="30">
+        <v>0</v>
+      </c>
+      <c r="I438" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A439" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B439" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C439" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D439" s="30">
+        <v>0</v>
+      </c>
+      <c r="E439" s="30">
+        <v>0</v>
+      </c>
+      <c r="F439" s="30">
+        <v>0</v>
+      </c>
+      <c r="G439" s="30">
+        <v>0</v>
+      </c>
+      <c r="H439" s="30">
+        <v>0</v>
+      </c>
+      <c r="I439" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A440" s="28">
+        <v>45179</v>
+      </c>
+      <c r="B440" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C440" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D440" s="30">
+        <v>0</v>
+      </c>
+      <c r="E440" s="30">
+        <v>0</v>
+      </c>
+      <c r="F440" s="30">
+        <v>0</v>
+      </c>
+      <c r="G440" s="30">
+        <v>0</v>
+      </c>
+      <c r="H440" s="30">
+        <v>0</v>
+      </c>
+      <c r="I440" s="30">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C422">
+  <conditionalFormatting sqref="C2:C440">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Scuri"</formula>
     </cfRule>
@@ -13741,13 +14309,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H422 D2:E422" xr:uid="{A2364708-0661-4544-87F1-D3FDEABF18B6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H440 D2:E440" xr:uid="{A2364708-0661-4544-87F1-D3FDEABF18B6}">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I422" xr:uid="{3C35827F-D598-4F40-B064-7FA732E53B67}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I440" xr:uid="{3C35827F-D598-4F40-B064-7FA732E53B67}">
       <formula1>"0, 1, 2, 3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:G422" xr:uid="{2FE2E49C-6CC7-4B84-9D73-A960B8BAAF9A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:G440" xr:uid="{2FE2E49C-6CC7-4B84-9D73-A960B8BAAF9A}">
       <formula1>"0, 1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Input/FantaSPL_V2.3.xlsx
+++ b/Input/FantaSPL_V2.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Local_Docs\Admin\Other\Kit\SPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FED7B2-5C3A-48DB-BF9B-73BBA4D962B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4E1AFA-F941-4F23-9A7F-4B7E86CDDF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="11" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Players!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Points!$A$1:$I$422</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Points!$A$1:$J$440</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="110">
   <si>
     <t>Parameter</t>
   </si>
@@ -218,9 +218,6 @@
   </si>
   <si>
     <t>Dario (Francesco)</t>
-  </si>
-  <si>
-    <t>Daniele (Francesco)</t>
   </si>
   <si>
     <t>Ale (Mazzu)</t>
@@ -996,7 +993,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="25">
         <v>0</v>
@@ -1108,7 +1105,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="25">
         <v>10</v>
@@ -1550,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -1909,7 +1906,7 @@
         <v>44938</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>30</v>
@@ -2228,7 +2225,7 @@
         <v>44945</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>30</v>
@@ -2542,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
@@ -2927,7 +2924,7 @@
         <v>44952</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>22</v>
@@ -2985,7 +2982,7 @@
         <v>44952</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>22</v>
@@ -3072,7 +3069,7 @@
         <v>44959</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>22</v>
@@ -3130,7 +3127,7 @@
         <v>44959</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>22</v>
@@ -3420,7 +3417,7 @@
         <v>44959</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>30</v>
@@ -3710,7 +3707,7 @@
         <v>44966</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>30</v>
@@ -3971,7 +3968,7 @@
         <v>44980</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>22</v>
@@ -4145,7 +4142,7 @@
         <v>44980</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>30</v>
@@ -4725,7 +4722,7 @@
         <v>44987</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C111" s="9" t="s">
         <v>22</v>
@@ -4899,7 +4896,7 @@
         <v>44994</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>30</v>
@@ -5015,7 +5012,7 @@
         <v>44994</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>22</v>
@@ -5044,7 +5041,7 @@
         <v>44994</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C122" s="9" t="s">
         <v>22</v>
@@ -5073,7 +5070,7 @@
         <v>44994</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>22</v>
@@ -5189,7 +5186,7 @@
         <v>45001</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C127" s="9" t="s">
         <v>22</v>
@@ -5334,7 +5331,7 @@
         <v>45001</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C132" s="9" t="s">
         <v>22</v>
@@ -5392,7 +5389,7 @@
         <v>45001</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C134" s="9" t="s">
         <v>30</v>
@@ -5769,7 +5766,7 @@
         <v>45008</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C147" s="9" t="s">
         <v>30</v>
@@ -5798,7 +5795,7 @@
         <v>45008</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>30</v>
@@ -5943,7 +5940,7 @@
         <v>45008</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>30</v>
@@ -6233,7 +6230,7 @@
         <v>45015</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C163" s="9" t="s">
         <v>30</v>
@@ -6262,7 +6259,7 @@
         <v>45015</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C164" s="9" t="s">
         <v>30</v>
@@ -6291,7 +6288,7 @@
         <v>45015</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>30</v>
@@ -6320,7 +6317,7 @@
         <v>45015</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C166" s="9" t="s">
         <v>30</v>
@@ -6755,7 +6752,7 @@
         <v>45022</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C181" s="9" t="s">
         <v>22</v>
@@ -6784,7 +6781,7 @@
         <v>45030</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C182" s="9" t="s">
         <v>30</v>
@@ -6958,7 +6955,7 @@
         <v>45030</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C188" s="9" t="s">
         <v>30</v>
@@ -7103,7 +7100,7 @@
         <v>45030</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C193" s="9" t="s">
         <v>22</v>
@@ -7219,7 +7216,7 @@
         <v>45030</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>22</v>
@@ -7306,7 +7303,7 @@
         <v>45030</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>22</v>
@@ -7335,7 +7332,7 @@
         <v>45030</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>22</v>
@@ -7480,7 +7477,7 @@
         <v>45050</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>22</v>
@@ -7567,7 +7564,7 @@
         <v>45050</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C209" s="9" t="s">
         <v>22</v>
@@ -7799,7 +7796,7 @@
         <v>45050</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>30</v>
@@ -7828,7 +7825,7 @@
         <v>45050</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>30</v>
@@ -8002,7 +7999,7 @@
         <v>45057</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C224" s="9" t="s">
         <v>30</v>
@@ -8031,7 +8028,7 @@
         <v>45057</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C225" s="9" t="s">
         <v>30</v>
@@ -8147,7 +8144,7 @@
         <v>45057</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C229" s="9" t="s">
         <v>22</v>
@@ -8234,7 +8231,7 @@
         <v>45057</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C232" s="9" t="s">
         <v>22</v>
@@ -8263,7 +8260,7 @@
         <v>45057</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C233" s="9" t="s">
         <v>22</v>
@@ -8408,7 +8405,7 @@
         <v>45064</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>22</v>
@@ -8437,7 +8434,7 @@
         <v>45064</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>22</v>
@@ -8466,7 +8463,7 @@
         <v>45064</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>22</v>
@@ -8495,7 +8492,7 @@
         <v>45064</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>22</v>
@@ -8582,7 +8579,7 @@
         <v>45064</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>30</v>
@@ -8611,7 +8608,7 @@
         <v>45064</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C245" s="9" t="s">
         <v>30</v>
@@ -8814,7 +8811,7 @@
         <v>45071</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>22</v>
@@ -8988,7 +8985,7 @@
         <v>45071</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>30</v>
@@ -9017,7 +9014,7 @@
         <v>45071</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>30</v>
@@ -9075,7 +9072,7 @@
         <v>45071</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>30</v>
@@ -9394,7 +9391,7 @@
         <v>45078</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C272" s="9" t="s">
         <v>30</v>
@@ -9452,7 +9449,7 @@
         <v>45078</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C274" s="9" t="s">
         <v>30</v>
@@ -9481,7 +9478,7 @@
         <v>45078</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C275" s="9" t="s">
         <v>30</v>
@@ -9539,7 +9536,7 @@
         <v>45078</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C277" s="9" t="s">
         <v>30</v>
@@ -9800,7 +9797,7 @@
         <v>45085</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>22</v>
@@ -9829,7 +9826,7 @@
         <v>45085</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>22</v>
@@ -9858,7 +9855,7 @@
         <v>45085</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C288" s="9" t="s">
         <v>22</v>
@@ -9887,7 +9884,7 @@
         <v>45085</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C289" s="9" t="s">
         <v>22</v>
@@ -9945,7 +9942,7 @@
         <v>45085</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C291" s="9" t="s">
         <v>22</v>
@@ -10061,7 +10058,7 @@
         <v>45092</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C295" s="9" t="s">
         <v>22</v>
@@ -10119,7 +10116,7 @@
         <v>45092</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C297" s="9" t="s">
         <v>22</v>
@@ -10148,7 +10145,7 @@
         <v>45092</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C298" s="9" t="s">
         <v>22</v>
@@ -10206,7 +10203,7 @@
         <v>45092</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C300" s="9" t="s">
         <v>30</v>
@@ -10264,7 +10261,7 @@
         <v>45092</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C302" s="9" t="s">
         <v>30</v>
@@ -10409,7 +10406,7 @@
         <v>45092</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C307" s="9" t="s">
         <v>30</v>
@@ -10496,7 +10493,7 @@
         <v>45099</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C310" s="9" t="s">
         <v>30</v>
@@ -10525,7 +10522,7 @@
         <v>45099</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C311" s="9" t="s">
         <v>30</v>
@@ -10583,7 +10580,7 @@
         <v>45099</v>
       </c>
       <c r="B313" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C313" s="9" t="s">
         <v>30</v>
@@ -10612,7 +10609,7 @@
         <v>45099</v>
       </c>
       <c r="B314" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C314" s="9" t="s">
         <v>30</v>
@@ -10786,7 +10783,7 @@
         <v>45099</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C320" s="9" t="s">
         <v>22</v>
@@ -10815,7 +10812,7 @@
         <v>45099</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C321" s="9" t="s">
         <v>22</v>
@@ -11076,7 +11073,7 @@
         <v>45106</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C330" s="9" t="s">
         <v>30</v>
@@ -11105,7 +11102,7 @@
         <v>45106</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C331" s="9" t="s">
         <v>30</v>
@@ -11163,7 +11160,7 @@
         <v>45106</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C333" s="9" t="s">
         <v>22</v>
@@ -11192,7 +11189,7 @@
         <v>45106</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C334" s="9" t="s">
         <v>22</v>
@@ -11221,7 +11218,7 @@
         <v>45106</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C335" s="9" t="s">
         <v>22</v>
@@ -11279,7 +11276,7 @@
         <v>45106</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C337" s="9" t="s">
         <v>22</v>
@@ -11395,7 +11392,7 @@
         <v>45113</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C341" s="9" t="s">
         <v>30</v>
@@ -11482,7 +11479,7 @@
         <v>45113</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C344" s="9" t="s">
         <v>30</v>
@@ -11511,7 +11508,7 @@
         <v>45113</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C345" s="9" t="s">
         <v>30</v>
@@ -11540,7 +11537,7 @@
         <v>45113</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C346" s="9" t="s">
         <v>30</v>
@@ -11743,7 +11740,7 @@
         <v>45113</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C353" s="9" t="s">
         <v>22</v>
@@ -11772,7 +11769,7 @@
         <v>45114</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C354" s="9" t="s">
         <v>22</v>
@@ -11859,7 +11856,7 @@
         <v>45114</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C357" s="9" t="s">
         <v>22</v>
@@ -11946,7 +11943,7 @@
         <v>45114</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C360" s="9" t="s">
         <v>22</v>
@@ -11975,7 +11972,7 @@
         <v>45114</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C361" s="9" t="s">
         <v>30</v>
@@ -12033,7 +12030,7 @@
         <v>45114</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C363" s="9" t="s">
         <v>30</v>
@@ -12062,7 +12059,7 @@
         <v>45114</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C364" s="9" t="s">
         <v>30</v>
@@ -12178,7 +12175,7 @@
         <v>45115</v>
       </c>
       <c r="B368" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C368" s="9" t="s">
         <v>30</v>
@@ -12207,7 +12204,7 @@
         <v>45115</v>
       </c>
       <c r="B369" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C369" s="9" t="s">
         <v>30</v>
@@ -12265,7 +12262,7 @@
         <v>45115</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C371" s="9" t="s">
         <v>30</v>
@@ -12294,7 +12291,7 @@
         <v>45115</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C372" s="9" t="s">
         <v>22</v>
@@ -12323,7 +12320,7 @@
         <v>45115</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C373" s="9" t="s">
         <v>22</v>
@@ -12410,7 +12407,7 @@
         <v>45115</v>
       </c>
       <c r="B376" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C376" s="9" t="s">
         <v>22</v>
@@ -12439,7 +12436,7 @@
         <v>45116</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C377" s="9" t="s">
         <v>30</v>
@@ -12497,7 +12494,7 @@
         <v>45116</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C379" s="9" t="s">
         <v>30</v>
@@ -12555,7 +12552,7 @@
         <v>45116</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C381" s="9" t="s">
         <v>30</v>
@@ -12584,7 +12581,7 @@
         <v>45116</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C382" s="9" t="s">
         <v>30</v>
@@ -12642,7 +12639,7 @@
         <v>45116</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C384" s="9" t="s">
         <v>22</v>
@@ -12700,7 +12697,7 @@
         <v>45116</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C386" s="9" t="s">
         <v>22</v>
@@ -12787,7 +12784,7 @@
         <v>45116</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C389" s="9" t="s">
         <v>22</v>
@@ -12874,7 +12871,7 @@
         <v>45117</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C392" s="9" t="s">
         <v>30</v>
@@ -12903,7 +12900,7 @@
         <v>45117</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C393" s="9" t="s">
         <v>30</v>
@@ -13019,7 +13016,7 @@
         <v>45117</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C397" s="9" t="s">
         <v>22</v>
@@ -13048,7 +13045,7 @@
         <v>45117</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C398" s="9" t="s">
         <v>22</v>
@@ -13077,7 +13074,7 @@
         <v>45117</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C399" s="9" t="s">
         <v>22</v>
@@ -13135,7 +13132,7 @@
         <v>45118</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C401" s="9" t="s">
         <v>30</v>
@@ -13193,7 +13190,7 @@
         <v>45118</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C403" s="9" t="s">
         <v>30</v>
@@ -13251,7 +13248,7 @@
         <v>45118</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C405" s="9" t="s">
         <v>30</v>
@@ -13309,7 +13306,7 @@
         <v>45118</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C407" s="9" t="s">
         <v>22</v>
@@ -13396,7 +13393,7 @@
         <v>45118</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C410" s="9" t="s">
         <v>22</v>
@@ -13483,7 +13480,7 @@
         <v>45118</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C413" s="9" t="s">
         <v>22</v>
@@ -13512,7 +13509,7 @@
         <v>45119</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C414" s="9" t="s">
         <v>30</v>
@@ -13570,7 +13567,7 @@
         <v>45119</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C416" s="9" t="s">
         <v>30</v>
@@ -13599,7 +13596,7 @@
         <v>45119</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C417" s="9" t="s">
         <v>30</v>
@@ -13657,7 +13654,7 @@
         <v>45119</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C419" s="9" t="s">
         <v>22</v>
@@ -13715,7 +13712,7 @@
         <v>45119</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C421" s="9" t="s">
         <v>22</v>
@@ -13744,7 +13741,7 @@
         <v>45119</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C422" s="9" t="s">
         <v>22</v>
@@ -13773,7 +13770,7 @@
         <v>45170</v>
       </c>
       <c r="B423" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C423" s="30" t="s">
         <v>30</v>
@@ -13797,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.35">
@@ -13834,7 +13831,7 @@
         <v>45170</v>
       </c>
       <c r="B425" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C425" s="30" t="s">
         <v>30</v>
@@ -13863,7 +13860,7 @@
         <v>45170</v>
       </c>
       <c r="B426" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C426" s="30" t="s">
         <v>30</v>
@@ -13921,7 +13918,7 @@
         <v>45170</v>
       </c>
       <c r="B428" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C428" s="30" t="s">
         <v>22</v>
@@ -13979,7 +13976,7 @@
         <v>45170</v>
       </c>
       <c r="B430" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C430" s="30" t="s">
         <v>22</v>
@@ -14008,7 +14005,7 @@
         <v>45170</v>
       </c>
       <c r="B431" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C431" s="30" t="s">
         <v>22</v>
@@ -14037,7 +14034,7 @@
         <v>45179</v>
       </c>
       <c r="B432" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C432" s="30" t="s">
         <v>30</v>
@@ -14061,7 +14058,7 @@
         <v>0</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.35">
@@ -14098,7 +14095,7 @@
         <v>45179</v>
       </c>
       <c r="B434" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C434" s="30" t="s">
         <v>30</v>
@@ -14122,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.35">
@@ -14130,7 +14127,7 @@
         <v>45179</v>
       </c>
       <c r="B435" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C435" s="30" t="s">
         <v>30</v>
@@ -14188,7 +14185,7 @@
         <v>45179</v>
       </c>
       <c r="B437" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C437" s="30" t="s">
         <v>22</v>
@@ -14246,7 +14243,7 @@
         <v>45179</v>
       </c>
       <c r="B439" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C439" s="30" t="s">
         <v>22</v>
@@ -14275,7 +14272,7 @@
         <v>45179</v>
       </c>
       <c r="B440" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C440" s="30" t="s">
         <v>22</v>
@@ -14300,6 +14297,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J440" xr:uid="{F55E8A24-46F9-4225-A2C2-A9164F13364A}"/>
   <conditionalFormatting sqref="C2:C440">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Scuri"</formula>
@@ -14352,36 +14350,36 @@
         <v>16</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>85</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="E2" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>29</v>
@@ -14389,19 +14387,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E3" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>26</v>
@@ -14409,19 +14407,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E4" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" s="19"/>
     </row>
@@ -14433,31 +14431,31 @@
         <v>42</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="E6" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>32</v>
@@ -14465,37 +14463,37 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="E8" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F8" s="19"/>
     </row>
@@ -14507,31 +14505,31 @@
         <v>21</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E9" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E10" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" s="19"/>
     </row>
@@ -14543,31 +14541,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E11" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="E12" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F12" s="19"/>
     </row>
@@ -14579,13 +14577,13 @@
         <v>31</v>
       </c>
       <c r="C13" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="E13" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F13" s="19"/>
     </row>
@@ -14597,31 +14595,31 @@
         <v>28</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="E14" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F15" s="19"/>
     </row>
@@ -14633,13 +14631,13 @@
         <v>37</v>
       </c>
       <c r="C16" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="E16" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F16" s="19" t="s">
         <v>23</v>
@@ -14653,13 +14651,13 @@
         <v>52</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="E17" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>33</v>
@@ -14673,49 +14671,49 @@
         <v>33</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F19" s="19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="E20" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>41</v>
@@ -14729,13 +14727,13 @@
         <v>57</v>
       </c>
       <c r="C21" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="E21" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>41</v>
@@ -14743,40 +14741,40 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="E22" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>97</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -14787,13 +14785,13 @@
         <v>43</v>
       </c>
       <c r="C24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="E24" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F24" s="19"/>
     </row>
@@ -14805,13 +14803,13 @@
         <v>51</v>
       </c>
       <c r="C25" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E25" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F25" s="19" t="s">
         <v>49</v>
@@ -14825,13 +14823,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E26" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F26" s="19"/>
     </row>
@@ -14840,37 +14838,37 @@
         <v>38</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E28" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -14881,13 +14879,13 @@
         <v>35</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F29" s="19"/>
     </row>
@@ -14899,13 +14897,13 @@
         <v>41</v>
       </c>
       <c r="C30" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E30" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F30" s="19"/>
     </row>
@@ -14917,31 +14915,31 @@
         <v>47</v>
       </c>
       <c r="C31" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E31" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="E32" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>23</v>
@@ -14955,13 +14953,13 @@
         <v>49</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F33" s="19"/>
     </row>
@@ -14973,13 +14971,13 @@
         <v>36</v>
       </c>
       <c r="C34" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="E34" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F34" s="19"/>
     </row>
@@ -14991,16 +14989,16 @@
         <v>56</v>
       </c>
       <c r="C35" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E35" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -15011,13 +15009,13 @@
         <v>32</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F36" s="19"/>
     </row>
@@ -15029,13 +15027,13 @@
         <v>55</v>
       </c>
       <c r="C37" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E37" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>45</v>
@@ -15043,19 +15041,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C38" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="E38" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F38" s="19"/>
     </row>
@@ -15064,16 +15062,16 @@
         <v>44</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F39" s="19"/>
     </row>
@@ -15085,13 +15083,13 @@
         <v>50</v>
       </c>
       <c r="C40" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E40" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F40" s="19" t="s">
         <v>49</v>
@@ -15099,19 +15097,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="E41" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F41" s="19" t="s">
         <v>45</v>
@@ -15119,19 +15117,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="E42" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F42" s="19"/>
     </row>
@@ -15143,31 +15141,31 @@
         <v>23</v>
       </c>
       <c r="C43" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E43" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F43" s="19"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E44" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="19"/>
     </row>
@@ -15179,31 +15177,31 @@
         <v>25</v>
       </c>
       <c r="C45" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="E45" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F45" s="19"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="E46" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F46" s="19" t="s">
         <v>26</v>
@@ -15217,51 +15215,51 @@
         <v>53</v>
       </c>
       <c r="C47" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="E47" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="E47" s="21" t="s">
-        <v>89</v>
-      </c>
       <c r="F47" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C48" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="E48" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F48" s="19"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="E49" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F49" s="19"/>
     </row>
@@ -15273,13 +15271,13 @@
         <v>26</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D50" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F50" s="19"/>
     </row>
@@ -15291,13 +15289,13 @@
         <v>48</v>
       </c>
       <c r="C51" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="E51" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F51" s="19"/>
     </row>
@@ -15309,31 +15307,31 @@
         <v>54</v>
       </c>
       <c r="C52" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E52" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F52" s="19"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E53" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F53" s="19"/>
     </row>
@@ -15345,13 +15343,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="E54" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F54" s="19"/>
     </row>
@@ -15363,13 +15361,13 @@
         <v>46</v>
       </c>
       <c r="C55" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E55" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>23</v>
@@ -15377,37 +15375,37 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="E56" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F56" s="19"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C57" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D57" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E57" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F57" s="19"/>
     </row>
@@ -15419,13 +15417,13 @@
         <v>40</v>
       </c>
       <c r="C58" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E58" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>33</v>
@@ -15439,13 +15437,13 @@
         <v>27</v>
       </c>
       <c r="C59" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="E59" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F59" s="19"/>
     </row>
@@ -15457,31 +15455,31 @@
         <v>45</v>
       </c>
       <c r="C60" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="E60" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F60" s="19"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C61" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E61" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>34</v>
@@ -15489,39 +15487,39 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C62" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="E62" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C63" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="E63" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F63" s="19"/>
     </row>
@@ -15533,49 +15531,49 @@
         <v>34</v>
       </c>
       <c r="C64" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="E64" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F64" s="19"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F65" s="19"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D66" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="E66" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="F66" s="19"/>
     </row>
@@ -15598,37 +15596,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Input/FantaSPL_V2.3.xlsx
+++ b/Input/FantaSPL_V2.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Local_Docs\Admin\Other\Kit\SPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4E1AFA-F941-4F23-9A7F-4B7E86CDDF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD84EDA-5A43-47D7-A73C-DA8243F3BB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{05F018D4-855F-4570-8D15-9B4DD092A228}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="11" r:id="rId1"/>
@@ -942,14 +942,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977A5798-2DE9-40A8-A5E2-5B00E9A9537A}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -963,7 +963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>4</v>
       </c>
@@ -977,7 +977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>109</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>6</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>7</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>9</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>10</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>11</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>20</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
         <v>107</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
         <v>12</v>
       </c>
@@ -1140,12 +1140,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A29AA2D-3F32-45F2-B719-A1F62E0F1A5F}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultColWidth="17.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="17.1796875" style="1"/>
+    <col min="1" max="3" width="17.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>44938</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>44945</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>44952</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>44959</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>44966</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>44980</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>44987</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>44994</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>45001</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>45008</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>45015</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>45022</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>45030</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>45050</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>45057</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>45064</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>45071</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>45078</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>45085</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>45092</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>45099</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>45106</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>45113</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>45114</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>45115</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>45116</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>45117</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>45118</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>45119</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>45170</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>45179</v>
       </c>
@@ -1505,20 +1505,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55E8A24-46F9-4225-A2C2-A9164F13364A}">
   <dimension ref="A1:J440"/>
-  <sheetFormatPr defaultColWidth="17.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="17.1796875" style="3"/>
+    <col min="8" max="8" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="17.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>44938</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>44938</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>44938</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>44938</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>44938</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>44938</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>44938</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>44938</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>44938</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>44938</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>44938</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>44938</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>44938</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>44938</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>44945</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>44945</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>44945</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>44945</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>44945</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>44945</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>44945</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>44945</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>44945</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>44945</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>44945</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>44945</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>44945</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>44945</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>44945</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>44945</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>44945</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>44945</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>44945</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>44945</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>44945</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>44945</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>44952</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>44952</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>44952</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>44952</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>44952</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>44952</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>44952</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>44952</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>44952</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>44952</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>44952</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>44952</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>44952</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>44952</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>44952</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>44952</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>44959</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>44959</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>44959</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>44959</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>44959</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>44959</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>44959</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>44959</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>44959</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>44959</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>44959</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>44959</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>44959</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>44959</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>44966</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>44966</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>44966</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>44966</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>44966</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>44966</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>44966</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>44966</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>44966</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>44966</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>44966</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>44966</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>44966</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>44966</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>44980</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>44980</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>44980</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>44980</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>44980</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>44980</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>44980</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>44980</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>44980</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>44980</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>44980</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>44980</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>44980</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>44980</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>44980</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>44980</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>44987</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>44987</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>44987</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>44987</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>44987</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>44987</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>44987</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>44987</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>44987</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>44987</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>44987</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>44987</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>44987</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>44987</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>44994</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>44994</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>44994</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>44994</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>44994</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>44994</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>44994</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>44994</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>44994</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>44994</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>44994</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>44994</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>44994</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>44994</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>45001</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>45001</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>45001</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>45001</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>45001</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <v>45001</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <v>45001</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <v>45001</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <v>45001</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <v>45001</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>45001</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
         <v>45001</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="7">
         <v>45001</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="7">
         <v>45001</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="7">
         <v>45008</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="7">
         <v>45008</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="7">
         <v>45008</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="7">
         <v>45008</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="7">
         <v>45008</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="7">
         <v>45008</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="7">
         <v>45008</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="7">
         <v>45008</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="7">
         <v>45008</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="7">
         <v>45008</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="7">
         <v>45008</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="7">
         <v>45008</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="7">
         <v>45008</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="7">
         <v>45008</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="7">
         <v>45015</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="7">
         <v>45015</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="7">
         <v>45015</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
         <v>45015</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>45015</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
         <v>45015</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
         <v>45015</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
         <v>45015</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>45015</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
         <v>45015</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
         <v>45015</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="7">
         <v>45015</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="7">
         <v>45015</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
         <v>45015</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
         <v>45022</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
         <v>45022</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
         <v>45022</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
         <v>45022</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
         <v>45022</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
         <v>45022</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
         <v>45022</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="7">
         <v>45022</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="7">
         <v>45022</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="7">
         <v>45022</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="7">
         <v>45022</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="7">
         <v>45022</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="7">
         <v>45022</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="7">
         <v>45022</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="7">
         <v>45030</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="7">
         <v>45030</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="7">
         <v>45030</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="7">
         <v>45030</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="7">
         <v>45030</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
         <v>45030</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
         <v>45030</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
         <v>45030</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
         <v>45030</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
         <v>45030</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
         <v>45030</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
         <v>45030</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>45030</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="7">
         <v>45030</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="7">
         <v>45030</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="7">
         <v>45030</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="7">
         <v>45030</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="7">
         <v>45030</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <v>45030</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="7">
         <v>45030</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="7">
         <v>45030</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="7">
         <v>45030</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="7">
         <v>45050</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="7">
         <v>45050</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="7">
         <v>45050</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="7">
         <v>45050</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="7">
         <v>45050</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="7">
         <v>45050</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="7">
         <v>45050</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="7">
         <v>45050</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="7">
         <v>45050</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="7">
         <v>45050</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="7">
         <v>45050</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="7">
         <v>45050</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="7">
         <v>45050</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="7">
         <v>45050</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="7">
         <v>45050</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="7">
         <v>45050</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="7">
         <v>45057</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="7">
         <v>45057</v>
       </c>
@@ -7936,7 +7936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="7">
         <v>45057</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="7">
         <v>45057</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="7">
         <v>45057</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="7">
         <v>45057</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="7">
         <v>45057</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="7">
         <v>45057</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="7">
         <v>45057</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="7">
         <v>45057</v>
       </c>
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="7">
         <v>45057</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="7">
         <v>45057</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="7">
         <v>45057</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="7">
         <v>45057</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="7">
         <v>45064</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="7">
         <v>45064</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="7">
         <v>45064</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="7">
         <v>45064</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="7">
         <v>45064</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="7">
         <v>45064</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="7">
         <v>45064</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="7">
         <v>45064</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="7">
         <v>45064</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="7">
         <v>45064</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="7">
         <v>45064</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="7">
         <v>45064</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="7">
         <v>45064</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="7">
         <v>45064</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="7">
         <v>45064</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="7">
         <v>45064</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="7">
         <v>45071</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="7">
         <v>45071</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="7">
         <v>45071</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="7">
         <v>45071</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="7">
         <v>45071</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="7">
         <v>45071</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="7">
         <v>45071</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="7">
         <v>45071</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="7">
         <v>45071</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="7">
         <v>45071</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="7">
         <v>45071</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="7">
         <v>45071</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="7">
         <v>45071</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="7">
         <v>45071</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="7">
         <v>45078</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="7">
         <v>45078</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="7">
         <v>45078</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="7">
         <v>45078</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="7">
         <v>45078</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="7">
         <v>45078</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="7">
         <v>45078</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="7">
         <v>45078</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="7">
         <v>45078</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="7">
         <v>45078</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="7">
         <v>45078</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="7">
         <v>45078</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="7">
         <v>45078</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="7">
         <v>45078</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="7">
         <v>45085</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="7">
         <v>45085</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="7">
         <v>45085</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="7">
         <v>45085</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="7">
         <v>45085</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="7">
         <v>45085</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="7">
         <v>45085</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="7">
         <v>45085</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="7">
         <v>45085</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="7">
         <v>45085</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="7">
         <v>45085</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="7">
         <v>45085</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="7">
         <v>45085</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="7">
         <v>45085</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="7">
         <v>45092</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="7">
         <v>45092</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="7">
         <v>45092</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="7">
         <v>45092</v>
       </c>
@@ -10082,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="7">
         <v>45092</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="7">
         <v>45092</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="7">
         <v>45092</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="7">
         <v>45092</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="7">
         <v>45092</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="7">
         <v>45092</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="7">
         <v>45092</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="7">
         <v>45092</v>
       </c>
@@ -10314,7 +10314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="7">
         <v>45092</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="7">
         <v>45092</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="7">
         <v>45092</v>
       </c>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="7">
         <v>45092</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="7">
         <v>45099</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="7">
         <v>45099</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="7">
         <v>45099</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="7">
         <v>45099</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="7">
         <v>45099</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="7">
         <v>45099</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="7">
         <v>45099</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="7">
         <v>45099</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="7">
         <v>45099</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="7">
         <v>45099</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="7">
         <v>45099</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="7">
         <v>45099</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="7">
         <v>45099</v>
       </c>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="7">
         <v>45099</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="7">
         <v>45099</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="7">
         <v>45099</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="7">
         <v>45106</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="7">
         <v>45106</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="7">
         <v>45106</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="7">
         <v>45106</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="7">
         <v>45106</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="7">
         <v>45106</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="7">
         <v>45106</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="7">
         <v>45106</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="7">
         <v>45106</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="7">
         <v>45106</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="7">
         <v>45106</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="7">
         <v>45106</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="7">
         <v>45106</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="7">
         <v>45106</v>
       </c>
@@ -11300,7 +11300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="7">
         <v>45106</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="7">
         <v>45106</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="7">
         <v>45113</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="7">
         <v>45113</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="7">
         <v>45113</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="7">
         <v>45113</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="7">
         <v>45113</v>
       </c>
@@ -11503,7 +11503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="7">
         <v>45113</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="7">
         <v>45113</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="7">
         <v>45113</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="7">
         <v>45113</v>
       </c>
@@ -11619,7 +11619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="7">
         <v>45113</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="7">
         <v>45113</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="7">
         <v>45113</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="7">
         <v>45113</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="7">
         <v>45113</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="7">
         <v>45114</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="7">
         <v>45114</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="7">
         <v>45114</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="7">
         <v>45114</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="7">
         <v>45114</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="7">
         <v>45114</v>
       </c>
@@ -11938,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="7">
         <v>45114</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="7">
         <v>45114</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="7">
         <v>45114</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="7">
         <v>45114</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="7">
         <v>45114</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="7">
         <v>45114</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="7">
         <v>45114</v>
       </c>
@@ -12141,7 +12141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="7">
         <v>45115</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="7">
         <v>45115</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="7">
         <v>45115</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="7">
         <v>45115</v>
       </c>
@@ -12257,7 +12257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="7">
         <v>45115</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="7">
         <v>45115</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="7">
         <v>45115</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="7">
         <v>45115</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="7">
         <v>45115</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="7">
         <v>45115</v>
       </c>
@@ -12431,7 +12431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" s="7">
         <v>45116</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" s="7">
         <v>45116</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" s="7">
         <v>45116</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" s="7">
         <v>45116</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" s="7">
         <v>45116</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" s="7">
         <v>45116</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" s="7">
         <v>45116</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" s="7">
         <v>45116</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" s="7">
         <v>45116</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" s="7">
         <v>45116</v>
       </c>
@@ -12721,7 +12721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" s="7">
         <v>45116</v>
       </c>
@@ -12750,7 +12750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" s="7">
         <v>45116</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" s="7">
         <v>45116</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" s="7">
         <v>45116</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" s="7">
         <v>45117</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" s="7">
         <v>45117</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" s="7">
         <v>45117</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" s="7">
         <v>45117</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" s="7">
         <v>45117</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" s="7">
         <v>45117</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" s="7">
         <v>45117</v>
       </c>
@@ -13040,7 +13040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" s="7">
         <v>45117</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" s="7">
         <v>45117</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" s="7">
         <v>45118</v>
       </c>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" s="7">
         <v>45118</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" s="7">
         <v>45118</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" s="7">
         <v>45118</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" s="7">
         <v>45118</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" s="7">
         <v>45118</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" s="7">
         <v>45118</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" s="7">
         <v>45118</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" s="7">
         <v>45118</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" s="7">
         <v>45118</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" s="7">
         <v>45118</v>
       </c>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" s="7">
         <v>45118</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" s="7">
         <v>45118</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" s="7">
         <v>45118</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" s="7">
         <v>45119</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" s="7">
         <v>45119</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" s="7">
         <v>45119</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" s="7">
         <v>45119</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" s="7">
         <v>45119</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" s="7">
         <v>45119</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" s="7">
         <v>45119</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" s="7">
         <v>45119</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" s="7">
         <v>45119</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" s="28">
         <v>45170</v>
       </c>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" s="28">
         <v>45170</v>
       </c>
@@ -13826,7 +13826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" s="28">
         <v>45170</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" s="28">
         <v>45170</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" s="28">
         <v>45170</v>
       </c>
@@ -13913,7 +13913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" s="28">
         <v>45170</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" s="28">
         <v>45170</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" s="28">
         <v>45170</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" s="28">
         <v>45170</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" s="28">
         <v>45179</v>
       </c>
@@ -14058,10 +14058,10 @@
         <v>0</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" s="28">
         <v>45179</v>
       </c>
@@ -14090,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" s="28">
         <v>45179</v>
       </c>
@@ -14119,10 +14119,10 @@
         <v>0</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" s="28">
         <v>45179</v>
       </c>
@@ -14151,7 +14151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" s="28">
         <v>45179</v>
       </c>
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" s="28">
         <v>45179</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" s="28">
         <v>45179</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" s="28">
         <v>45179</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" s="28">
         <v>45179</v>
       </c>
@@ -14337,15 +14337,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E168A56-6341-4406-8D41-CC351A3A492A}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr defaultColWidth="25.54296875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="25.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="25.54296875" style="20"/>
-    <col min="3" max="5" width="25.54296875" style="22"/>
-    <col min="6" max="6" width="25.54296875" style="20"/>
-    <col min="7" max="16384" width="25.54296875" style="17"/>
+    <col min="1" max="2" width="25.5703125" style="20"/>
+    <col min="3" max="5" width="25.5703125" style="22"/>
+    <col min="6" max="6" width="25.5703125" style="20"/>
+    <col min="7" max="16384" width="25.5703125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>74</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>58</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>68</v>
       </c>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="F4" s="19"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>42</v>
       </c>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F5" s="19"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>71</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>70</v>
       </c>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="F7" s="19"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>78</v>
       </c>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="F8" s="19"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>21</v>
       </c>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="F9" s="19"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
         <v>80</v>
       </c>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="F10" s="19"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>39</v>
       </c>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="F11" s="19"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
         <v>64</v>
       </c>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="F12" s="19"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>31</v>
       </c>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="F13" s="19"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>28</v>
       </c>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="F14" s="19"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>73</v>
       </c>
@@ -14623,7 +14623,7 @@
       </c>
       <c r="F15" s="19"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
         <v>37</v>
       </c>
@@ -14643,7 +14643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>52</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
         <v>33</v>
       </c>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="F18" s="19"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
         <v>94</v>
       </c>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F19" s="19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>95</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
         <v>57</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
         <v>79</v>
       </c>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="F22" s="19"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
         <v>96</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>43</v>
       </c>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="F24" s="19"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
         <v>51</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>29</v>
       </c>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="F26" s="19"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>38</v>
       </c>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="F27" s="19"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>99</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>35</v>
       </c>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="F29" s="19"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>41</v>
       </c>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="F30" s="19"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>47</v>
       </c>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="F31" s="19"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
         <v>72</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
         <v>49</v>
       </c>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="F33" s="19"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="19" t="s">
         <v>36</v>
       </c>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F34" s="19"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="19" t="s">
         <v>56</v>
       </c>
@@ -15001,7 +15001,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="F36" s="19"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="19" t="s">
         <v>55</v>
       </c>
@@ -15039,7 +15039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="18" t="s">
         <v>66</v>
       </c>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="F38" s="19"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="19" t="s">
         <v>44</v>
       </c>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F39" s="19"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
         <v>50</v>
       </c>
@@ -15095,7 +15095,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="19" t="s">
         <v>61</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="19" t="s">
         <v>63</v>
       </c>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F42" s="19"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>23</v>
       </c>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="F43" s="19"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="18" t="s">
         <v>60</v>
       </c>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="F44" s="19"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
         <v>25</v>
       </c>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F45" s="19"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="18" t="s">
         <v>69</v>
       </c>
@@ -15207,7 +15207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="19" t="s">
         <v>53</v>
       </c>
@@ -15227,7 +15227,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="19" t="s">
         <v>76</v>
       </c>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="F48" s="19"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="19" t="s">
         <v>62</v>
       </c>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="F49" s="19"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="19" t="s">
         <v>26</v>
       </c>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="F50" s="19"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="19" t="s">
         <v>48</v>
       </c>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="F51" s="19"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="19" t="s">
         <v>54</v>
       </c>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="F52" s="19"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="18" t="s">
         <v>67</v>
       </c>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F53" s="19"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="19" t="s">
         <v>24</v>
       </c>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="F54" s="19"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
         <v>46</v>
       </c>
@@ -15373,7 +15373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="18" t="s">
         <v>59</v>
       </c>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="F56" s="19"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="19" t="s">
         <v>103</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="F57" s="19"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="19" t="s">
         <v>40</v>
       </c>
@@ -15429,7 +15429,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="19" t="s">
         <v>27</v>
       </c>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="19" t="s">
         <v>45</v>
       </c>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="F60" s="19"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="19" t="s">
         <v>104</v>
       </c>
@@ -15485,7 +15485,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>105</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="19" t="s">
         <v>77</v>
       </c>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="F63" s="19"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="19" t="s">
         <v>34</v>
       </c>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="F64" s="19"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="19" t="s">
         <v>75</v>
       </c>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="F65" s="19"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="19" t="s">
         <v>65</v>
       </c>
@@ -15589,42 +15589,42 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B62ADB2D-FAA1-4F57-93BE-5AA80A69D8E9}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>88</v>
       </c>
